--- a/output/pdf_financials_xlsx/WERX.xlsx
+++ b/output/pdf_financials_xlsx/WERX.xlsx
@@ -2572,7 +2572,7 @@
         </is>
       </c>
       <c r="B103" s="3" t="n">
-        <v>0</v>
+        <v>-0.001354</v>
       </c>
       <c r="C103" s="1" t="inlineStr">
         <is>
@@ -2580,10 +2580,10 @@
         </is>
       </c>
       <c r="D103" s="3" t="n">
-        <v>0</v>
+        <v>-0.0004929999999999999</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>0</v>
+        <v>-0.013997</v>
       </c>
     </row>
     <row r="104">
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.219205</v>
+        <v>0.217851</v>
       </c>
       <c r="C106" s="1" t="inlineStr">
         <is>
@@ -2643,10 +2643,10 @@
         </is>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.274908</v>
+        <v>0.274415</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0.11526</v>
+        <v>0.101263</v>
       </c>
     </row>
     <row r="107">
@@ -3460,7 +3460,11 @@
           <t>Prepaids and deposit</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>-</t>
@@ -4424,7 +4428,11 @@
           <t>Prepaids and deposit</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E31" s="5" t="n">
         <v>-0.001354</v>
       </c>

--- a/output/pdf_financials_xlsx/WERX.xlsx
+++ b/output/pdf_financials_xlsx/WERX.xlsx
@@ -666,7 +666,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.010342</v>
       </c>
     </row>
     <row r="13">
@@ -993,7 +993,7 @@
         <v>-0.414313</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.959324</v>
+        <v>-0.969666</v>
       </c>
     </row>
     <row r="28">
@@ -1035,7 +1035,7 @@
         <v>-0.414313</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.959324</v>
+        <v>-0.969666</v>
       </c>
     </row>
     <row r="30">
@@ -1056,7 +1056,7 @@
         <v>-254.6625197460216</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-4638.67317827958</v>
+        <v>-4688.680431313766</v>
       </c>
     </row>
     <row r="31">
@@ -1120,7 +1120,7 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.726846</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0.485503</v>
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.726846</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>0.485503</v>
@@ -1414,7 +1414,7 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.7282</v>
+        <v>0.001354</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0</v>
@@ -3946,7 +3946,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -6562,7 +6562,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">

--- a/output/pdf_financials_xlsx/WERX.xlsx
+++ b/output/pdf_financials_xlsx/WERX.xlsx
@@ -1756,13 +1756,13 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.006484</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.06487900000000001</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.151259</v>
       </c>
     </row>
     <row r="65">
@@ -1819,13 +1819,13 @@
         </is>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.013917</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.029076</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.072548</v>
       </c>
     </row>
     <row r="68">
